--- a/tables/Cq_model_results.xlsx
+++ b/tables/Cq_model_results.xlsx
@@ -7,21 +7,43 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Fixed_effects" sheetId="1" r:id="rId1"/>
-    <sheet name="Type_III_ANOVA" sheetId="2" r:id="rId2"/>
-    <sheet name="EMM_Sample_type" sheetId="3" r:id="rId3"/>
-    <sheet name="EMM_Temperature" sheetId="4" r:id="rId4"/>
-    <sheet name="EMM_Timepoint" sheetId="5" r:id="rId5"/>
-    <sheet name="Pairs_Sample_type" sheetId="6" r:id="rId6"/>
-    <sheet name="Pairs_Temperature" sheetId="7" r:id="rId7"/>
-    <sheet name="Pairs_Timepoint" sheetId="8" r:id="rId8"/>
+    <sheet name="Cq_detection" sheetId="1" r:id="rId1"/>
+    <sheet name="Fixed_effects" sheetId="2" r:id="rId2"/>
+    <sheet name="Type_III_ANOVA" sheetId="3" r:id="rId3"/>
+    <sheet name="EMM_Sample_type" sheetId="4" r:id="rId4"/>
+    <sheet name="EMM_Temperature" sheetId="5" r:id="rId5"/>
+    <sheet name="EMM_Timepoint" sheetId="6" r:id="rId6"/>
+    <sheet name="Pairs_Sample_type" sheetId="7" r:id="rId7"/>
+    <sheet name="Pairs_Temperature" sheetId="8" r:id="rId8"/>
+    <sheet name="Pairs_Timepoint" sheetId="9" r:id="rId9"/>
+    <sheet name="Variance_components" sheetId="10" r:id="rId10"/>
+    <sheet name="Model_diagnostics" sheetId="11" r:id="rId11"/>
+    <sheet name="Model_summary" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="88">
+  <si>
+    <t>Total_specimens</t>
+  </si>
+  <si>
+    <t>RABV_RNA_detected</t>
+  </si>
+  <si>
+    <t>Not_detected</t>
+  </si>
+  <si>
+    <t>Detection_percentage</t>
+  </si>
+  <si>
+    <t>Minimum_Cq</t>
+  </si>
+  <si>
+    <t>Maximum_Cq</t>
+  </si>
   <si>
     <t>term</t>
   </si>
@@ -146,6 +168,9 @@
     <t>upper.CL</t>
   </si>
   <si>
+    <t>t.ratio</t>
+  </si>
+  <si>
     <t>FTA</t>
   </si>
   <si>
@@ -173,9 +198,6 @@
     <t>contrast</t>
   </si>
   <si>
-    <t>t.ratio</t>
-  </si>
-  <si>
     <t>FTA - RDT</t>
   </si>
   <si>
@@ -198,6 +220,75 @@
   </si>
   <si>
     <t>timepoint7 - timepoint21</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Sample ID random-intercept variance</t>
+  </si>
+  <si>
+    <t>Residual variance</t>
+  </si>
+  <si>
+    <t>ICC</t>
+  </si>
+  <si>
+    <t>ICC (%)</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>P_value</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>DHARMa uniformity</t>
+  </si>
+  <si>
+    <t>Asymptotic one-sample Kolmogorov-Smirnov test</t>
+  </si>
+  <si>
+    <t>DHARMa dispersion</t>
+  </si>
+  <si>
+    <t>DHARMa nonparametric dispersion test via sd of residuals fitted vs. simulated</t>
+  </si>
+  <si>
+    <t>DHARMa outliers</t>
+  </si>
+  <si>
+    <t>DHARMa outlier test based on exact binomial test with approximate expectations</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Number of observations</t>
+  </si>
+  <si>
+    <t>Number of sample IDs</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>Log-likelihood</t>
+  </si>
+  <si>
+    <t>Residual standard deviation</t>
   </si>
 </sst>
 </file>
@@ -540,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
@@ -564,323 +655,205 @@
       </c>
     </row>
     <row r="2" spans="1:6">
+      <c r="A2">
+        <v>160</v>
+      </c>
+      <c r="B2">
+        <v>140</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>87.5</v>
+      </c>
+      <c r="E2">
+        <v>14.16</v>
+      </c>
+      <c r="F2">
+        <v>31.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="B2">
-        <v>-1.018</v>
+        <v>8.048</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3">
+        <v>1.512</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4">
+        <v>0.842</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5">
+        <v>84.18600000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2">
+        <v>0.08699999999999999</v>
       </c>
       <c r="C2">
-        <v>1.383</v>
-      </c>
-      <c r="D2">
-        <v>-4.479</v>
-      </c>
-      <c r="E2">
-        <v>2.443</v>
-      </c>
-      <c r="F2">
-        <v>0.492</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.595</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="B3">
-        <v>5.55</v>
+        <v>0.973</v>
       </c>
       <c r="C3">
-        <v>0.778</v>
-      </c>
-      <c r="D3">
-        <v>3.993</v>
-      </c>
-      <c r="E3">
-        <v>7.107</v>
-      </c>
-      <c r="F3">
-        <v>1.73E-09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.828</v>
-      </c>
-      <c r="D4">
-        <v>-1.587</v>
-      </c>
-      <c r="E4">
-        <v>1.727</v>
-      </c>
-      <c r="F4">
-        <v>0.9330000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4">
+        <v>280.579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="B5">
-        <v>0.43</v>
-      </c>
-      <c r="C5">
-        <v>0.778</v>
-      </c>
-      <c r="D5">
-        <v>-1.127</v>
-      </c>
-      <c r="E5">
-        <v>1.987</v>
-      </c>
-      <c r="F5">
-        <v>0.582</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>1.218</v>
-      </c>
-      <c r="C6">
-        <v>0.778</v>
-      </c>
-      <c r="D6">
-        <v>-0.339</v>
-      </c>
-      <c r="E6">
-        <v>2.775</v>
-      </c>
-      <c r="F6">
-        <v>0.123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-122.29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B7">
-        <v>2.782</v>
-      </c>
-      <c r="C7">
-        <v>0.778</v>
-      </c>
-      <c r="D7">
-        <v>1.225</v>
-      </c>
-      <c r="E7">
-        <v>4.339</v>
-      </c>
-      <c r="F7">
-        <v>0.000709</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>-0.774</v>
-      </c>
-      <c r="C8">
-        <v>1.136</v>
-      </c>
-      <c r="D8">
-        <v>-3.047</v>
-      </c>
-      <c r="E8">
-        <v>1.5</v>
-      </c>
-      <c r="F8">
-        <v>0.498</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>0.09</v>
-      </c>
-      <c r="C9">
-        <v>1.1</v>
-      </c>
-      <c r="D9">
-        <v>-2.111</v>
-      </c>
-      <c r="E9">
-        <v>2.291</v>
-      </c>
-      <c r="F9">
-        <v>0.9350000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>-0.966</v>
-      </c>
-      <c r="C10">
-        <v>1.1</v>
-      </c>
-      <c r="D10">
-        <v>-3.167</v>
-      </c>
-      <c r="E10">
-        <v>1.235</v>
-      </c>
-      <c r="F10">
-        <v>0.383</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>-1.18</v>
-      </c>
-      <c r="C11">
-        <v>1.1</v>
-      </c>
-      <c r="D11">
-        <v>-3.381</v>
-      </c>
-      <c r="E11">
-        <v>1.021</v>
-      </c>
-      <c r="F11">
-        <v>0.288</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>-0.006</v>
-      </c>
-      <c r="C12">
-        <v>1.136</v>
-      </c>
-      <c r="D12">
-        <v>-2.279</v>
-      </c>
-      <c r="E12">
-        <v>2.268</v>
-      </c>
-      <c r="F12">
-        <v>0.996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
-        <v>-1.12</v>
-      </c>
-      <c r="C13">
-        <v>1.136</v>
-      </c>
-      <c r="D13">
-        <v>-3.393</v>
-      </c>
-      <c r="E13">
-        <v>1.154</v>
-      </c>
-      <c r="F13">
-        <v>0.328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>-1.354</v>
-      </c>
-      <c r="C14">
-        <v>1.136</v>
-      </c>
-      <c r="D14">
-        <v>-3.627</v>
-      </c>
-      <c r="E14">
-        <v>0.92</v>
-      </c>
-      <c r="F14">
-        <v>0.238</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
-        <v>-0.092</v>
-      </c>
-      <c r="C15">
-        <v>1.581</v>
-      </c>
-      <c r="D15">
-        <v>-3.257</v>
-      </c>
-      <c r="E15">
-        <v>3.072</v>
-      </c>
-      <c r="F15">
-        <v>0.954</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
-        <v>1.683</v>
-      </c>
-      <c r="C16">
-        <v>1.605</v>
-      </c>
-      <c r="D16">
-        <v>-1.53</v>
-      </c>
-      <c r="E16">
-        <v>4.897</v>
-      </c>
-      <c r="F16">
-        <v>0.299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17">
-        <v>1.246</v>
-      </c>
-      <c r="C17">
-        <v>1.581</v>
-      </c>
-      <c r="D17">
-        <v>-1.919</v>
-      </c>
-      <c r="E17">
-        <v>4.41</v>
-      </c>
-      <c r="F17">
-        <v>0.434</v>
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>
@@ -890,191 +863,347 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>-1.018</v>
+      </c>
+      <c r="C2">
+        <v>1.383</v>
+      </c>
+      <c r="D2">
+        <v>-4.479</v>
+      </c>
+      <c r="E2">
+        <v>2.443</v>
+      </c>
+      <c r="F2">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <v>5.55</v>
+      </c>
+      <c r="C3">
+        <v>0.778</v>
+      </c>
+      <c r="D3">
+        <v>3.993</v>
+      </c>
+      <c r="E3">
+        <v>7.107</v>
+      </c>
+      <c r="F3">
+        <v>1.73E-09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C4">
+        <v>0.828</v>
+      </c>
+      <c r="D4">
+        <v>-1.587</v>
+      </c>
+      <c r="E4">
+        <v>1.727</v>
+      </c>
+      <c r="F4">
+        <v>0.9330000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.43</v>
+      </c>
+      <c r="C5">
+        <v>0.778</v>
+      </c>
+      <c r="D5">
+        <v>-1.127</v>
+      </c>
+      <c r="E5">
+        <v>1.987</v>
+      </c>
+      <c r="F5">
+        <v>0.582</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>1.218</v>
+      </c>
+      <c r="C6">
+        <v>0.778</v>
+      </c>
+      <c r="D6">
+        <v>-0.339</v>
+      </c>
+      <c r="E6">
+        <v>2.775</v>
+      </c>
+      <c r="F6">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>2.782</v>
+      </c>
+      <c r="C7">
+        <v>0.778</v>
+      </c>
+      <c r="D7">
+        <v>1.225</v>
+      </c>
+      <c r="E7">
+        <v>4.339</v>
+      </c>
+      <c r="F7">
+        <v>0.000709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>-0.774</v>
+      </c>
+      <c r="C8">
+        <v>1.136</v>
+      </c>
+      <c r="D8">
+        <v>-3.047</v>
+      </c>
+      <c r="E8">
+        <v>1.5</v>
+      </c>
+      <c r="F8">
+        <v>0.498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>0.09</v>
+      </c>
+      <c r="C9">
+        <v>1.1</v>
+      </c>
+      <c r="D9">
+        <v>-2.111</v>
+      </c>
+      <c r="E9">
+        <v>2.291</v>
+      </c>
+      <c r="F9">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>-0.966</v>
+      </c>
+      <c r="C10">
+        <v>1.1</v>
+      </c>
+      <c r="D10">
+        <v>-3.167</v>
+      </c>
+      <c r="E10">
+        <v>1.235</v>
+      </c>
+      <c r="F10">
+        <v>0.383</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>-1.18</v>
+      </c>
+      <c r="C11">
+        <v>1.1</v>
+      </c>
+      <c r="D11">
+        <v>-3.381</v>
+      </c>
+      <c r="E11">
+        <v>1.021</v>
+      </c>
+      <c r="F11">
+        <v>0.288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B12">
+        <v>-0.006</v>
+      </c>
+      <c r="C12">
+        <v>1.136</v>
+      </c>
+      <c r="D12">
+        <v>-2.279</v>
+      </c>
+      <c r="E12">
+        <v>2.268</v>
+      </c>
+      <c r="F12">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B13">
+        <v>-1.12</v>
+      </c>
+      <c r="C13">
+        <v>1.136</v>
+      </c>
+      <c r="D13">
+        <v>-3.393</v>
+      </c>
+      <c r="E13">
+        <v>1.154</v>
+      </c>
+      <c r="F13">
+        <v>0.328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B14">
+        <v>-1.354</v>
+      </c>
+      <c r="C14">
+        <v>1.136</v>
+      </c>
+      <c r="D14">
+        <v>-3.627</v>
+      </c>
+      <c r="E14">
+        <v>0.92</v>
+      </c>
+      <c r="F14">
+        <v>0.238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B15">
+        <v>-0.092</v>
+      </c>
+      <c r="C15">
+        <v>1.581</v>
+      </c>
+      <c r="D15">
+        <v>-3.257</v>
+      </c>
+      <c r="E15">
+        <v>3.072</v>
+      </c>
+      <c r="F15">
+        <v>0.954</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B16">
+        <v>1.683</v>
+      </c>
+      <c r="C16">
+        <v>1.605</v>
+      </c>
+      <c r="D16">
+        <v>-1.53</v>
+      </c>
+      <c r="E16">
+        <v>4.897</v>
+      </c>
+      <c r="F16">
+        <v>0.299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2">
-        <v>484.344</v>
-      </c>
-      <c r="C2">
-        <v>484.344</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>57.999</v>
-      </c>
-      <c r="F2">
-        <v>320.356</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3">
-        <v>6.567</v>
-      </c>
-      <c r="C3">
-        <v>6.567</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>57.998</v>
-      </c>
-      <c r="F3">
-        <v>4.344</v>
-      </c>
-      <c r="G3">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4">
-        <v>35.961</v>
-      </c>
-      <c r="C4">
-        <v>11.987</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>57.999</v>
-      </c>
-      <c r="F4">
-        <v>7.928</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5">
-        <v>0.02</v>
-      </c>
-      <c r="C5">
-        <v>0.02</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>57.999</v>
-      </c>
-      <c r="F5">
-        <v>0.013</v>
-      </c>
-      <c r="G5">
-        <v>0.909</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6">
-        <v>1.122</v>
-      </c>
-      <c r="C6">
-        <v>0.374</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>57.998</v>
-      </c>
-      <c r="F6">
-        <v>0.247</v>
-      </c>
-      <c r="G6">
-        <v>0.863</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7">
-        <v>1.642</v>
-      </c>
-      <c r="C7">
-        <v>0.547</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>57.999</v>
-      </c>
-      <c r="F7">
-        <v>0.362</v>
-      </c>
-      <c r="G7">
-        <v>0.781</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8">
-        <v>2.866</v>
-      </c>
-      <c r="C8">
-        <v>0.955</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>57.998</v>
-      </c>
-      <c r="F8">
-        <v>0.632</v>
-      </c>
-      <c r="G8">
-        <v>0.597</v>
+      <c r="B17">
+        <v>1.246</v>
+      </c>
+      <c r="C17">
+        <v>1.581</v>
+      </c>
+      <c r="D17">
+        <v>-1.919</v>
+      </c>
+      <c r="E17">
+        <v>4.41</v>
+      </c>
+      <c r="F17">
+        <v>0.434</v>
       </c>
     </row>
   </sheetData>
@@ -1084,67 +1213,191 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2">
+        <v>484.344</v>
+      </c>
+      <c r="C2">
+        <v>484.344</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>57.999</v>
+      </c>
+      <c r="F2">
+        <v>320.356</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3">
+        <v>6.567</v>
+      </c>
+      <c r="C3">
+        <v>6.567</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>57.998</v>
+      </c>
+      <c r="F3">
+        <v>4.344</v>
+      </c>
+      <c r="G3">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4">
+        <v>35.961</v>
+      </c>
+      <c r="C4">
+        <v>11.987</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>57.999</v>
+      </c>
+      <c r="F4">
+        <v>7.928</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5">
+        <v>0.02</v>
+      </c>
+      <c r="C5">
+        <v>0.02</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>57.999</v>
+      </c>
+      <c r="F5">
+        <v>0.013</v>
+      </c>
+      <c r="G5">
+        <v>0.909</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B6">
+        <v>1.122</v>
+      </c>
+      <c r="C6">
+        <v>0.374</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>57.998</v>
+      </c>
+      <c r="F6">
+        <v>0.247</v>
+      </c>
+      <c r="G6">
+        <v>0.863</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="B7">
+        <v>1.642</v>
+      </c>
+      <c r="C7">
+        <v>0.547</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>57.999</v>
+      </c>
+      <c r="F7">
+        <v>0.362</v>
+      </c>
+      <c r="G7">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>41</v>
       </c>
-      <c r="B2">
-        <v>-0.1855377255354705</v>
-      </c>
-      <c r="C2">
-        <v>1.284035159429088</v>
-      </c>
-      <c r="D2">
-        <v>4.096406184483324</v>
-      </c>
-      <c r="E2">
-        <v>-3.717744449871184</v>
-      </c>
-      <c r="F2">
-        <v>3.346668998800243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3">
-        <v>4.818194525562382</v>
-      </c>
-      <c r="C3">
-        <v>1.284035159429088</v>
-      </c>
-      <c r="D3">
-        <v>4.096406184483323</v>
-      </c>
-      <c r="E3">
-        <v>1.28598780122667</v>
-      </c>
-      <c r="F3">
-        <v>8.350401249898095</v>
+      <c r="B8">
+        <v>2.866</v>
+      </c>
+      <c r="C8">
+        <v>0.955</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>57.998</v>
+      </c>
+      <c r="F8">
+        <v>0.632</v>
+      </c>
+      <c r="G8">
+        <v>0.597</v>
       </c>
     </row>
   </sheetData>
@@ -1154,67 +1407,85 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B2">
-        <v>2.607499999999974</v>
+        <v>-0.1855377255354705</v>
       </c>
       <c r="C2">
-        <v>1.283544296808377</v>
+        <v>1.284035159429088</v>
       </c>
       <c r="D2">
-        <v>4.090161051389876</v>
+        <v>4.096406184483324</v>
       </c>
       <c r="E2">
-        <v>-0.9254221821804345</v>
+        <v>-3.717744449871184</v>
       </c>
       <c r="F2">
-        <v>6.140422182180383</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>3.346668998800243</v>
+      </c>
+      <c r="G2">
+        <v>-0.1444958295518675</v>
+      </c>
+      <c r="H2">
+        <v>0.891940308905588</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B3">
-        <v>2.025156800026938</v>
+        <v>4.818194525562382</v>
       </c>
       <c r="C3">
-        <v>1.284509468224798</v>
+        <v>1.284035159429088</v>
       </c>
       <c r="D3">
-        <v>4.102452528377738</v>
+        <v>4.096406184483323</v>
       </c>
       <c r="E3">
-        <v>-1.506361005469822</v>
+        <v>1.28598780122667</v>
       </c>
       <c r="F3">
-        <v>5.556674605523698</v>
+        <v>8.350401249898095</v>
+      </c>
+      <c r="G3">
+        <v>3.752385197695571</v>
+      </c>
+      <c r="H3">
+        <v>0.01906890794403112</v>
       </c>
     </row>
   </sheetData>
@@ -1224,107 +1495,85 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B2">
-        <v>1.598424548929084</v>
+        <v>2.607499999999974</v>
       </c>
       <c r="C2">
-        <v>1.300124852831078</v>
+        <v>1.283544296808377</v>
       </c>
       <c r="D2">
-        <v>4.305212556834412</v>
+        <v>4.090161051389876</v>
       </c>
       <c r="E2">
-        <v>-1.912581754064462</v>
+        <v>-0.9254221821804345</v>
       </c>
       <c r="F2">
-        <v>5.10943085192263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>6.140422182180383</v>
+      </c>
+      <c r="G2">
+        <v>2.031484231969015</v>
+      </c>
+      <c r="H2">
+        <v>0.1104757652235382</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B3">
-        <v>2.047499999999975</v>
+        <v>2.025156800026938</v>
       </c>
       <c r="C3">
-        <v>1.298184623936806</v>
+        <v>1.284509468224798</v>
       </c>
       <c r="D3">
-        <v>4.279678123206716</v>
+        <v>4.102452528377738</v>
       </c>
       <c r="E3">
-        <v>-1.465817893233093</v>
+        <v>-1.506361005469822</v>
       </c>
       <c r="F3">
-        <v>5.560817893233043</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4">
-        <v>2.194389051124789</v>
-      </c>
-      <c r="C4">
-        <v>1.300124852831079</v>
-      </c>
-      <c r="D4">
-        <v>4.305212556834408</v>
-      </c>
-      <c r="E4">
-        <v>-1.31661725186876</v>
-      </c>
-      <c r="F4">
-        <v>5.705395354118339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5">
-        <v>3.424999999999974</v>
-      </c>
-      <c r="C5">
-        <v>1.298184623936806</v>
-      </c>
-      <c r="D5">
-        <v>4.279678123206719</v>
-      </c>
-      <c r="E5">
-        <v>-0.08831789323309325</v>
-      </c>
-      <c r="F5">
-        <v>6.938317893233041</v>
+        <v>5.556674605523698</v>
+      </c>
+      <c r="G3">
+        <v>1.576599355725824</v>
+      </c>
+      <c r="H3">
+        <v>0.1882529586392461</v>
       </c>
     </row>
   </sheetData>
@@ -1334,47 +1583,137 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2">
-        <v>-5.003732251097852</v>
+        <v>1.598424548929084</v>
       </c>
       <c r="C2">
-        <v>0.2795664767931156</v>
+        <v>1.300124852831078</v>
       </c>
       <c r="D2">
-        <v>58.00373443535221</v>
+        <v>4.305212556834412</v>
       </c>
       <c r="E2">
-        <v>-17.89818403299014</v>
+        <v>-1.912581754064462</v>
       </c>
       <c r="F2">
-        <v>2.710206198887282E-25</v>
+        <v>5.10943085192263</v>
+      </c>
+      <c r="G2">
+        <v>1.229439269196681</v>
+      </c>
+      <c r="H2">
+        <v>0.2818314222799116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>2.047499999999975</v>
+      </c>
+      <c r="C3">
+        <v>1.298184623936806</v>
+      </c>
+      <c r="D3">
+        <v>4.279678123206716</v>
+      </c>
+      <c r="E3">
+        <v>-1.465817893233093</v>
+      </c>
+      <c r="F3">
+        <v>5.560817893233043</v>
+      </c>
+      <c r="G3">
+        <v>1.577202473551747</v>
+      </c>
+      <c r="H3">
+        <v>0.1852509259562448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4">
+        <v>2.194389051124789</v>
+      </c>
+      <c r="C4">
+        <v>1.300124852831079</v>
+      </c>
+      <c r="D4">
+        <v>4.305212556834408</v>
+      </c>
+      <c r="E4">
+        <v>-1.31661725186876</v>
+      </c>
+      <c r="F4">
+        <v>5.705395354118339</v>
+      </c>
+      <c r="G4">
+        <v>1.687829477566259</v>
+      </c>
+      <c r="H4">
+        <v>0.161627722828469</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5">
+        <v>3.424999999999974</v>
+      </c>
+      <c r="C5">
+        <v>1.298184623936806</v>
+      </c>
+      <c r="D5">
+        <v>4.279678123206719</v>
+      </c>
+      <c r="E5">
+        <v>-0.08831789323309325</v>
+      </c>
+      <c r="F5">
+        <v>6.938317893233041</v>
+      </c>
+      <c r="G5">
+        <v>2.638299619982788</v>
+      </c>
+      <c r="H5">
+        <v>0.05383970732773397</v>
       </c>
     </row>
   </sheetData>
@@ -1384,47 +1723,59 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2">
-        <v>0.5823431999730364</v>
+        <v>-5.003732251097852</v>
       </c>
       <c r="C2">
-        <v>0.2794160410626265</v>
+        <v>0.2795664767931156</v>
       </c>
       <c r="D2">
-        <v>58.00210057021125</v>
+        <v>58.00373443535221</v>
       </c>
       <c r="E2">
-        <v>2.08414376554177</v>
+        <v>-5.563344588564286</v>
       </c>
       <c r="F2">
-        <v>0.04156162993693848</v>
+        <v>-4.444119913631418</v>
+      </c>
+      <c r="G2">
+        <v>-17.89818403299014</v>
+      </c>
+      <c r="H2">
+        <v>2.710206198887282E-25</v>
       </c>
     </row>
   </sheetData>
@@ -1434,32 +1785,100 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
+    <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="B2">
+        <v>0.5823431999730364</v>
+      </c>
+      <c r="C2">
+        <v>0.2794160410626265</v>
+      </c>
+      <c r="D2">
+        <v>58.00210057021125</v>
+      </c>
+      <c r="E2">
+        <v>0.02303165649740846</v>
+      </c>
+      <c r="F2">
+        <v>1.141654743448664</v>
+      </c>
+      <c r="G2">
+        <v>2.08414376554177</v>
+      </c>
+      <c r="H2">
+        <v>0.04156162993693848</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>59</v>
       </c>
       <c r="B2">
         <v>-0.4490754510708909</v>
@@ -1471,15 +1890,21 @@
         <v>58.00291796946203</v>
       </c>
       <c r="E2">
+        <v>-1.494580889357916</v>
+      </c>
+      <c r="F2">
+        <v>0.5964299872161338</v>
+      </c>
+      <c r="G2">
         <v>-1.136151042559296</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>0.6688911501196627</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>-0.5959645021957055</v>
@@ -1491,15 +1916,21 @@
         <v>58.00723008290372</v>
       </c>
       <c r="E3">
+        <v>-1.658755815547531</v>
+      </c>
+      <c r="F3">
+        <v>0.4668268111561195</v>
+      </c>
+      <c r="G3">
         <v>-1.483250490171355</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>0.454044024369325</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>-1.82657545107089</v>
@@ -1511,15 +1942,21 @@
         <v>58.00291796946181</v>
       </c>
       <c r="E4">
+        <v>-2.872080889357985</v>
+      </c>
+      <c r="F4">
+        <v>-0.7810700127837955</v>
+      </c>
+      <c r="G4">
         <v>-4.621195832679367</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>0.000125366785479919</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <v>-0.1468890511248146</v>
@@ -1531,15 +1968,21 @@
         <v>58.00291796946159</v>
       </c>
       <c r="E5">
+        <v>-1.192394489411841</v>
+      </c>
+      <c r="F5">
+        <v>0.8986163871622115</v>
+      </c>
+      <c r="G5">
         <v>-0.3716260779297396</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>0.9823117922153081</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>-1.377499999999999</v>
@@ -1551,15 +1994,21 @@
         <v>58.00000068825659</v>
       </c>
       <c r="E6">
+        <v>-2.406000247293273</v>
+      </c>
+      <c r="F6">
+        <v>-0.3489997527067257</v>
+      </c>
+      <c r="G6">
         <v>-3.542671646864759</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>0.004278461658412502</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>-1.230610948875184</v>
@@ -1571,9 +2020,15 @@
         <v>58.00291796946159</v>
       </c>
       <c r="E7">
+        <v>-2.276116387162211</v>
+      </c>
+      <c r="F7">
+        <v>-0.1851055105881578</v>
+      </c>
+      <c r="G7">
         <v>-3.113418712190331</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>0.01481924279415814</v>
       </c>
     </row>
